--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,8 +86,9 @@
   <si>
     <t>Intention (das „Warum") einer onkologischen Therapielinie bzw. eines Behandlungsabschnitts.
 Verwendet aktuelle SNOMED-CT-Codes aus der Hierarchie `362961001 | Procedure by intent`.
-Die deutschen Anzeigetexte sind als Concept-Display hinterlegt (Übersetzung der englischen
-SNOMED-FSN). Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
+Als Concept-Display dient der englische SNOMED-Anzeigetext des aktuellen Release (validierbar
+gegen tx.fhir.org); die deutschen Begriffe stehen in den Label-Texten
+des Leitfadens. Extensible gebunden – seltene Sonderintentionen dürfen ergänzt werden.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -108,31 +109,31 @@
     <t>373808002</t>
   </si>
   <si>
-    <t>Kurativ</t>
+    <t>Curative - procedure intent</t>
   </si>
   <si>
     <t>363676003</t>
   </si>
   <si>
-    <t>Palliativ</t>
+    <t>Palliative intent</t>
   </si>
   <si>
     <t>373847000</t>
   </si>
   <si>
-    <t>Neoadjuvant</t>
+    <t>Neoadjuvant intent</t>
   </si>
   <si>
     <t>373846009</t>
   </si>
   <si>
-    <t>Adjuvant</t>
+    <t>Adjuvant - intent</t>
   </si>
   <si>
     <t>399707004</t>
   </si>
   <si>
-    <t>Supportiv</t>
+    <t>Supportive - procedure intent</t>
   </si>
   <si>
     <t/>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
+++ b/1.0.0-ballot/ValueSet-onko-therapy-intent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
